--- a/pharmacy_forms/018_hand_hygiene_observation_form--pharmacy_forms.xlsx
+++ b/pharmacy_forms/018_hand_hygiene_observation_form--pharmacy_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="23" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -520,12 +520,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>patient_name</t>
+          <t>patient_info</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>patient_name</t>
+          <t>Patient Information</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -548,7 +548,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>date_observed</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -566,12 +566,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>observed_by</t>
+          <t>observation_by</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>observed_by</t>
+          <t>Observed By</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>observed_at</t>
+          <t>hand_washing_technique</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>observed_at</t>
+          <t>Hand Washing Technique</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>observed_time</t>
+          <t>hand_washing_location</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>observed_time</t>
+          <t>Hand Washing Location</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>handwashing_technique</t>
+          <t>hand_washing_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>handwashing_technique</t>
+          <t>Hand Washing Frequency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>handwashing_technique_other</t>
+          <t>hand_washing_duration</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>Hand Washing Duration</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>handwashing_location</t>
+          <t>hand_washing_other_location</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>handwashing_location</t>
+          <t>Other Location</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>handwashing_frequent</t>
+          <t>hand_washing_other_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>handwashing_frequent</t>
+          <t>Other Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>handwashing_duration</t>
+          <t>hand_washing_other_duration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>handwashing_duration</t>
+          <t>Other Duration</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>handwashing_frequency</t>
+          <t>observation_completed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>handwashing_frequency</t>
+          <t>Observed Completed</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,17 +768,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>observation_completed</t>
+          <t>hand_washing_comments</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>observation_completed</t>
+          <t>Hand Washing Comments</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>observed_by</t>
+          <t>Completed By</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>observed_at</t>
+          <t>Completed At</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -837,17 +837,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>comments</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>notes</t>
+          <t>Comments</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>handwashing_technique_other</t>
+          <t>hand_washing_other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>other_technique</t>
+          <t>Other</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>handwashing_frequency_other</t>
+          <t>handwashing_frequency_comments</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>other_frequency</t>
+          <t>Comments Frequency</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,177 +911,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>handwashing_duration_other</t>
+          <t>hand_washing_duration_comments</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>other_duration</t>
+          <t>Comments Duration</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>handwashing_location_other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>other_location</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>handwashing_other</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>handwashing_comments</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>handwashing_frequency_comments</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>comments_frequency</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>handwashing_duration_comments</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>comments_duration</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>handwashing_location_comments</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>comments_location</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>handwashing_other_comments</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>comments</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,10 +937,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C15"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="32" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
     <col width="37" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1126,7 +965,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>handwashing_technique_choices</t>
+          <t>hand_washing_technique_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1143,7 +982,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>handwashing_technique_choices</t>
+          <t>hand_washing_technique_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1160,7 +999,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>handwashing_technique_choices</t>
+          <t>hand_washing_technique_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1177,7 +1016,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>handwashing_location_choices</t>
+          <t>hand_washing_location_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1194,7 +1033,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>handwashing_location_choices</t>
+          <t>hand_washing_location_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1211,153 +1050,85 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>handwashing_location_choices</t>
+          <t>hand_washing_location_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>bathroom_sink_(handwashing_station)</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Bathroom Sink (Handwashing Station)</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>handwashing_location_choices</t>
+          <t>hand_washing_frequency_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>handwashing_frequent_choices</t>
+          <t>hand_washing_frequency_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>frequently</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Frequently</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>handwashing_frequent_choices</t>
+          <t>hand_washing_frequency_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>handwashing_frequent_choices</t>
+          <t>hand_washing_frequency_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>handwashing_frequent_choices</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
           <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>handwashing_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>before_patient_contact</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Before Patient Contact</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>handwashing_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>after_patient_contact</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>After Patient Contact</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>handwashing_frequency_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>before_and_after_patient_contact</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Before and After Patient Contact</t>
         </is>
       </c>
     </row>
